--- a/export/n_r_10_n/v3.xlsx
+++ b/export/n_r_10_n/v3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="נוכחות B" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נוכחות B" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +27,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="002C3E50"/>
       <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -43,12 +48,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -97,21 +107,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -479,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -493,382 +509,454 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>שם העובד:</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>דוד לוי</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>סה"כ ימי עבודה לחודש:</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>סה"כ שעות חודשיות:</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>32:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>מחיר לשעה:</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>סה"כ לתשלום:</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1049.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>כרטיס עובד לחודש:</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>01/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>יום</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>כניסה</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>יציאה</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>הערה</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>1/1/23</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>08:01</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>3:12</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2:52</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>איחור קל</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>2/1/23</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>3:22</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>3:02</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>3/1/23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>3:07</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>איחור קל</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>4/1/23</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>08:01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>11:03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>3:02</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>איחור קל</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4/1/23</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>08:16</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>5/1/23</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>2:52</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5/1/23</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3:02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>איחור קל</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>6/1/23</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>3:12</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>7/1/23</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>8/1/23</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>ראשון</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>3:17</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>9/1/23</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3:02</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>10/1/23</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2:52</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11/1/23</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2:57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>12/1/23</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2:57</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>6/1/23</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2:47</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>7/1/23</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>8/1/23</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ראשון</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>3:17</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>9/1/23</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>3:02</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>10/1/23</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2:52</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>11/1/23</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>2:57</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>12/1/23</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2:57</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>33:47</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>32:47</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/export/n_r_10_n/v3.xlsx
+++ b/export/n_r_10_n/v3.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>32:47</t>
+          <t>32:28</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1049.07</t>
+          <t>1038.93</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>01/2023</t>
+          <t>1/23</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1/1/23</t>
+          <t>1/1/2023</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2/1/23</t>
+          <t>2/1/2023</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3/1/23</t>
+          <t>3/1/2023</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>3:07</t>
+          <t>2:58</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>4/1/23</t>
+          <t>4/1/2023</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3:02</t>
+          <t>2:58</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>5/1/23</t>
+          <t>5/1/2023</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>6/1/23</t>
+          <t>6/1/2023</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>7/1/23</t>
+          <t>7/1/2023</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>8/1/23</t>
+          <t>8/1/2023</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3:17</t>
+          <t>3:16</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -833,7 +833,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>9/1/23</t>
+          <t>9/1/2023</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>3:02</t>
+          <t>2:57</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>10/1/23</t>
+          <t>10/1/2023</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>11/1/23</t>
+          <t>11/1/2023</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>12/1/23</t>
+          <t>12/1/2023</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -953,7 +953,7 @@
       <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>32:47</t>
+          <t>32:28</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
